--- a/8 - BTS SIO - Annexe 8-1 - Tableau de synthe╠Çse - Epreuve E5 - 2025 1.xlsx
+++ b/8 - BTS SIO - Annexe 8-1 - Tableau de synthe╠Çse - Epreuve E5 - 2025 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loulo\Desktop\PORTFOLIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18FA0BE-BFE8-45AD-844B-690A331E1650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE0A8BB-3384-4C13-B3F6-8B93D92ECD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,12 +40,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
-  </si>
-  <si>
-    <t>SESSION 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
@@ -184,7 +181,22 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : file:///C:/Users/loulo/Desktop/PORTFOLIO/index.html</t>
+    <t>Adresse URL du portfolio : https://julien-portfolio.pages.dev</t>
+  </si>
+  <si>
+    <t>21/11/2025-28/11/2025</t>
+  </si>
+  <si>
+    <t>Déploiement d’une Stack Web avec Docker et Load Balancer</t>
+  </si>
+  <si>
+    <t>Mise en place et gestion de modèle d'IA (SLM) sur des serveurs proxmox pour répondre à des besoins,</t>
+  </si>
+  <si>
+    <t>05/01/2026-20/02/2026</t>
+  </si>
+  <si>
+    <t>SESSION 2026</t>
   </si>
 </sst>
 </file>
@@ -194,7 +206,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -274,6 +286,17 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="28"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -674,7 +697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -759,9 +782,48 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -786,44 +848,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1161,124 +1196,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H1" s="29"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="35"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="48"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="18" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="48"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="B6" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="28"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="G7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="H7" s="20" t="s">
         <v>21</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>22</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1317,16 +1352,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
+      <c r="A8" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="32"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1365,20 +1400,22 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="C9" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>26</v>
-      </c>
       <c r="D9" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
+      <c r="G9" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="H9" s="15"/>
       <c r="I9"/>
       <c r="J9"/>
@@ -1418,19 +1455,21 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>28</v>
-      </c>
       <c r="C10" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="14"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>25</v>
+      </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10"/>
@@ -1471,21 +1510,19 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>30</v>
-      </c>
       <c r="C11" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="14"/>
-      <c r="F11" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="F11" s="24"/>
       <c r="G11" s="14"/>
       <c r="H11" s="15"/>
       <c r="I11"/>
@@ -1526,21 +1563,21 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>26</v>
+      <c r="C12" s="52" t="s">
+        <v>25</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="14"/>
       <c r="G12" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" s="15"/>
       <c r="I12"/>
@@ -1581,22 +1618,18 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>26</v>
-      </c>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="15"/>
@@ -1637,13 +1670,23 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
+      <c r="A14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49" t="s">
+        <v>25</v>
+      </c>
       <c r="H14" s="15"/>
       <c r="I14"/>
       <c r="J14"/>
@@ -1862,16 +1905,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="A19" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1910,22 +1953,22 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="26" t="s">
-        <v>37</v>
-      </c>
       <c r="C20" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -1965,22 +2008,22 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="14"/>
       <c r="F21" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="14"/>
-      <c r="H21" s="25" t="s">
-        <v>26</v>
+      <c r="H21" s="50" t="s">
+        <v>25</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -2244,16 +2287,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="42"/>
-      <c r="C27" s="42"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
+      <c r="A27" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="35"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2291,14 +2334,26 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15"/>
+      <c r="A28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="51" t="s">
+        <v>25</v>
+      </c>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2711,6 +2766,11 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2718,16 +2778,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>